--- a/source/Lotto023.xlsx
+++ b/source/Lotto023.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d251688e3d9c1650/Cursor_AI_Project/Lotto_v200/source/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d251688e3d9c1650/Antigravity/Lotto_v200/source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EFEB642B-4A11-4F4A-B4C6-CFE4AA0DD5DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{EFEB642B-4A11-4F4A-B4C6-CFE4AA0DD5DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25647DF7-4089-4680-BBFB-494EE66FC508}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F22FEE7D-536D-4318-A667-B7B45F414D53}"/>
   </bookViews>
@@ -20,12 +20,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="14">
   <si>
     <t>회차</t>
-  </si>
-  <si>
-    <t>세트</t>
   </si>
   <si>
     <t>게임</t>
@@ -65,9 +62,6 @@
   </si>
   <si>
     <t>수동</t>
-  </si>
-  <si>
-    <t>반자동</t>
   </si>
 </sst>
 </file>
@@ -1039,10 +1033,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4286BA2D-2749-4702-A9D0-A8C69CDB0F73}">
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="5.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="12" width="6.25" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1079,11 +1078,8 @@
       <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1195</v>
       </c>
@@ -1091,7 +1087,7 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -1099,40 +1095,37 @@
       <c r="E2">
         <v>0</v>
       </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
+      </c>
+      <c r="I2">
         <v>13</v>
       </c>
-      <c r="H2">
-        <v>3</v>
-      </c>
-      <c r="I2">
-        <v>5</v>
-      </c>
       <c r="J2">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K2">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="L2">
-        <v>21</v>
-      </c>
-      <c r="M2">
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1195</v>
       </c>
       <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
         <v>1</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1140,40 +1133,37 @@
       <c r="E3">
         <v>1</v>
       </c>
-      <c r="F3">
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3">
         <v>1</v>
       </c>
-      <c r="G3" t="s">
-        <v>14</v>
-      </c>
       <c r="H3">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="I3">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J3">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="K3">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L3">
-        <v>37</v>
-      </c>
-      <c r="M3">
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1195</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4">
         <v>2</v>
@@ -1181,40 +1171,37 @@
       <c r="E4">
         <v>2</v>
       </c>
-      <c r="F4">
-        <v>2</v>
-      </c>
-      <c r="G4" t="s">
-        <v>15</v>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4">
+        <v>3</v>
       </c>
       <c r="H4">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I4">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="J4">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="K4">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="L4">
-        <v>41</v>
-      </c>
-      <c r="M4">
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1195</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5">
         <v>3</v>
@@ -1222,73 +1209,67 @@
       <c r="E5">
         <v>3</v>
       </c>
-      <c r="F5">
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5">
         <v>3</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5">
         <v>13</v>
       </c>
-      <c r="H5">
-        <v>3</v>
-      </c>
       <c r="I5">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="J5">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K5">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L5">
-        <v>37</v>
-      </c>
-      <c r="M5">
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1195</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
         <v>4</v>
       </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6" t="s">
-        <v>14</v>
+      <c r="F6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6">
+        <v>15</v>
       </c>
       <c r="H6">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I6">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J6">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="K6">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="L6">
-        <v>35</v>
-      </c>
-      <c r="M6">
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1194</v>
       </c>
@@ -1296,130 +1277,121 @@
         <v>1</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
         <v>5</v>
       </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
+      <c r="F7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7">
         <v>5</v>
       </c>
-      <c r="G7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H7">
-        <v>3</v>
-      </c>
       <c r="I7">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J7">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K7">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="L7">
-        <v>21</v>
-      </c>
-      <c r="M7">
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1194</v>
       </c>
       <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8">
         <v>1</v>
       </c>
-      <c r="C8">
-        <v>2</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8" t="s">
-        <v>13</v>
-      </c>
       <c r="H8">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="I8">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J8">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="K8">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L8">
-        <v>37</v>
-      </c>
-      <c r="M8">
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1194</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9">
         <v>3</v>
       </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9" t="s">
-        <v>14</v>
-      </c>
       <c r="H9">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I9">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="J9">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="K9">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="L9">
-        <v>41</v>
-      </c>
-      <c r="M9">
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1194</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C10">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -1427,40 +1399,37 @@
       <c r="E10">
         <v>0</v>
       </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10" t="s">
-        <v>15</v>
+      <c r="F10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10">
+        <v>3</v>
       </c>
       <c r="H10">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I10">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="J10">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K10">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L10">
-        <v>37</v>
-      </c>
-      <c r="M10">
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1194</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C11">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -1468,28 +1437,25 @@
       <c r="E11">
         <v>0</v>
       </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11" t="s">
-        <v>13</v>
+      <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11">
+        <v>15</v>
       </c>
       <c r="H11">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I11">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J11">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="K11">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="L11">
-        <v>35</v>
-      </c>
-      <c r="M11">
         <v>39</v>
       </c>
     </row>
